--- a/coronavirus_response_forms/020_coronavirus_self_assessment_form--coronavirus_response_forms.xlsx
+++ b/coronavirus_response_forms/020_coronavirus_self_assessment_form--coronavirus_response_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>shortness_of_breath</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Shortness of Breath</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>shortness_of_breath</t>
+          <t>muscle_pain</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Shortness of Breath</t>
+          <t>Muscle Pain</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>muscle_pain</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Muscle Pain</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nausea</t>
+          <t>vomiting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nausea</t>
+          <t>Vomiting</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>vomiting</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vomiting</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>diarrhea</t>
+          <t>abdominal_pain</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Diarrhea</t>
+          <t>Abdominal Pain</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>contact_tracing_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>abdominal_pain</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Abdominal Pain</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>contact_tracing_choices</t>
+          <t>recent_events_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>event_1</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Event 1</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>event_2</t>
+          <t>event_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Event 2</t>
+          <t>Event 3</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>event_3</t>
+          <t>event_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Event 3</t>
+          <t>Event 4</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>event_4</t>
+          <t>event_5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Event 4</t>
+          <t>Event 5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>recent_events_choices</t>
+          <t>travel_destination_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>event_5</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Event 5</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>travel_destination_choices</t>
+          <t>self_isolated_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>self_isolated_choices</t>
+          <t>medical_condition_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>medical_condition_choices</t>
+          <t>medical_history_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>medical_history_choices</t>
+          <t>test_results_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1590,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>test_results_choices</t>
+          <t>treatment_status_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>treatment_status_choices</t>
+          <t>hospitalization_status_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1658,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>hospitalization_status_choices</t>
+          <t>submit_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1692,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>submit_choices</t>
+          <t>self_assessment_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1726,27 +1726,10 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>self_assessment_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
         <is>
           <t>Option 2</t>
         </is>
